--- a/results/5Fold_metabric.xlsx
+++ b/results/5Fold_metabric.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,25 +513,25 @@
         <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6853265353655982</v>
+        <v>0.6851144096155588</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6409953476514005</v>
+        <v>0.6574056680300291</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7071740750441873</v>
+        <v>0.7190549395073237</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2227014080283235</v>
+        <v>0.2115023776299223</v>
       </c>
       <c r="L2" t="n">
-        <v>0.329488605260849</v>
+        <v>0.3331914752721786</v>
       </c>
     </row>
     <row r="3">
@@ -560,22 +560,22 @@
         <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6857359663176498</v>
+        <v>0.6853263536046892</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6584400180201805</v>
+        <v>0.6590625400046688</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7176943892454217</v>
+        <v>0.7208756674824555</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2196974584932213</v>
+        <v>0.2059081654712699</v>
       </c>
       <c r="L3" t="n">
-        <v>0.329160726070404</v>
+        <v>0.4148557275533676</v>
       </c>
     </row>
     <row r="4">
@@ -601,25 +601,25 @@
         <v>100</v>
       </c>
       <c r="F4" t="n">
-        <v>2025</v>
+        <v>42</v>
       </c>
       <c r="G4" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6885853240120544</v>
+        <v>0.6851522627362707</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6547445191573281</v>
+        <v>0.6580719771434472</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7194694163814631</v>
+        <v>0.7200526882421505</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2222492864777658</v>
+        <v>0.2072603515428221</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3287219345569611</v>
+        <v>0.4324391067028046</v>
       </c>
     </row>
     <row r="5">
@@ -645,25 +645,25 @@
         <v>100</v>
       </c>
       <c r="F5" t="n">
-        <v>114514</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>0.687459567655731</v>
+        <v>0.6852111597742561</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6693463014148475</v>
+        <v>0.6591803976350494</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7051050366190009</v>
+        <v>0.7202031425995108</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2201447488959713</v>
+        <v>0.207476608735608</v>
       </c>
       <c r="L5" t="n">
-        <v>0.328633114695549</v>
+        <v>0.4342531204223633</v>
       </c>
     </row>
     <row r="6">
@@ -674,7 +674,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ordsurv</t>
+          <t>deepsurv</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -689,25 +689,25 @@
         <v>100</v>
       </c>
       <c r="F6" t="n">
-        <v>777</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6849805140208457</v>
+        <v>0.6757184370594498</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6549527486790258</v>
+        <v>0.6579954264657134</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7221814980995405</v>
+        <v>0.7060674500847708</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2267200021816793</v>
+        <v>0.446644704356126</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3289659231901169</v>
+        <v>4.449938774108887</v>
       </c>
     </row>
     <row r="7">
@@ -733,25 +733,25 @@
         <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6778009716605726</v>
+        <v>0.6757184370594498</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6469936539465078</v>
+        <v>0.6579954264657134</v>
       </c>
       <c r="J7" t="n">
-        <v>0.706659738684017</v>
+        <v>0.7137536649691784</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4420582538211454</v>
+        <v>0.446641704183309</v>
       </c>
       <c r="L7" t="n">
-        <v>4.452223205566407</v>
+        <v>4.449938774108887</v>
       </c>
     </row>
     <row r="8">
@@ -780,7 +780,7 @@
         <v>42</v>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
         <v>0.6757184370594498</v>
@@ -789,10 +789,10 @@
         <v>0.6579954264657134</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7124176792736087</v>
+        <v>0.7145067385624891</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4466830722181915</v>
+        <v>0.4434569244779911</v>
       </c>
       <c r="L8" t="n">
         <v>4.449938774108887</v>
@@ -821,25 +821,25 @@
         <v>100</v>
       </c>
       <c r="F9" t="n">
-        <v>2025</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>25</v>
+        <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>0.681517880277472</v>
+        <v>0.6757184370594498</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6568242707765587</v>
+        <v>0.6579954264657134</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7128914617349931</v>
+        <v>0.7145081700449222</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4375155757882879</v>
+        <v>0.3836243031937542</v>
       </c>
       <c r="L9" t="n">
-        <v>4.443024063110352</v>
+        <v>4.449938774108887</v>
       </c>
     </row>
     <row r="10">
@@ -850,7 +850,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>deepsurv</t>
+          <t>deephit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -865,25 +865,25 @@
         <v>100</v>
       </c>
       <c r="F10" t="n">
-        <v>114514</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6780632645639977</v>
+        <v>0.6788827826411156</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6661602072260557</v>
+        <v>0.6621284758876136</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6992096892760241</v>
+        <v>0.7123501538725441</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4519752590025569</v>
+        <v>0.1741471157322882</v>
       </c>
       <c r="L10" t="n">
-        <v>4.441550636291504</v>
+        <v>0.8672354400157929</v>
       </c>
     </row>
     <row r="11">
@@ -894,7 +894,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>deepsurv</t>
+          <t>deephit</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -909,25 +909,25 @@
         <v>100</v>
       </c>
       <c r="F11" t="n">
-        <v>777</v>
+        <v>42</v>
       </c>
       <c r="G11" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6738161309327568</v>
+        <v>0.6717036839632774</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6461998116317488</v>
+        <v>0.6565061056168784</v>
       </c>
       <c r="J11" t="n">
-        <v>0.708452595454218</v>
+        <v>0.7085901505685523</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4334768692987822</v>
+        <v>0.170758191938917</v>
       </c>
       <c r="L11" t="n">
-        <v>4.456241607666016</v>
+        <v>1.431685543060303</v>
       </c>
     </row>
     <row r="12">
@@ -953,25 +953,25 @@
         <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5628684340492367</v>
+        <v>0.6642166876812399</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5502729240400027</v>
+        <v>0.653430539045236</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7108437489113886</v>
+        <v>0.6968215321563297</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1758289672562358</v>
+        <v>0.1725948339477735</v>
       </c>
       <c r="L12" t="n">
-        <v>1.078629648685455</v>
+        <v>2.4206538438797</v>
       </c>
     </row>
     <row r="13">
@@ -1000,22 +1000,22 @@
         <v>42</v>
       </c>
       <c r="G13" t="n">
-        <v>25</v>
+        <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5609475164679415</v>
+        <v>0.6630521758328521</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5454354801537897</v>
+        <v>0.6481060859343771</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7132504080952471</v>
+        <v>0.6929289803879387</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1708549630700373</v>
+        <v>0.1758329173611995</v>
       </c>
       <c r="L13" t="n">
-        <v>1.073342627286911</v>
+        <v>3.024437260627747</v>
       </c>
     </row>
     <row r="14">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>deephit</t>
+          <t>nll</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1041,25 +1041,25 @@
         <v>100</v>
       </c>
       <c r="F14" t="n">
-        <v>2025</v>
+        <v>42</v>
       </c>
       <c r="G14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5618225827887104</v>
+        <v>0.6780574900462607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.5452511946520684</v>
+        <v>0.6549709592945619</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7172183115831963</v>
+        <v>0.712919375959258</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1717839746085424</v>
+        <v>0.1821889046687757</v>
       </c>
       <c r="L14" t="n">
-        <v>1.076874685287476</v>
+        <v>1.350551307201385</v>
       </c>
     </row>
     <row r="15">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>deephit</t>
+          <t>nll</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1085,25 +1085,25 @@
         <v>100</v>
       </c>
       <c r="F15" t="n">
-        <v>114514</v>
+        <v>42</v>
       </c>
       <c r="G15" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5627919104293809</v>
+        <v>0.6572303966039603</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5476233239879378</v>
+        <v>0.6209742868887984</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7042272462572872</v>
+        <v>0.6835594590495031</v>
       </c>
       <c r="K15" t="n">
-        <v>0.173923720632017</v>
+        <v>0.1901345793011509</v>
       </c>
       <c r="L15" t="n">
-        <v>1.072924596071243</v>
+        <v>2.482987880706787</v>
       </c>
     </row>
     <row r="16">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>deephit</t>
+          <t>nll</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1129,25 +1129,25 @@
         <v>100</v>
       </c>
       <c r="F16" t="n">
-        <v>777</v>
+        <v>42</v>
       </c>
       <c r="G16" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5667112848375626</v>
+        <v>0.4757320535010973</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5548338718197809</v>
+        <v>0.4604358748735067</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7204655436620838</v>
+        <v>0.5014177184295301</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1769312850639808</v>
+        <v>0.4450699951902063</v>
       </c>
       <c r="L16" t="n">
-        <v>1.073465240001678</v>
+        <v>10.79922571182251</v>
       </c>
     </row>
     <row r="17">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>discrete</t>
+          <t>nll</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1173,25 +1173,25 @@
         <v>100</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="G17" t="n">
-        <v>25</v>
+        <v>10000</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6797823304223375</v>
+        <v>0.4166454165481115</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6327306360268532</v>
+        <v>0.3936419895209072</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7091588642527988</v>
+        <v>0.4973203471745656</v>
       </c>
       <c r="K17" t="n">
-        <v>0.190113912046979</v>
+        <v>0.5277352216456485</v>
       </c>
       <c r="L17" t="n">
-        <v>1.775596106052399</v>
+        <v>12.587864112854</v>
       </c>
     </row>
     <row r="18">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>discrete</t>
+          <t>lassocox</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1220,22 +1220,22 @@
         <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>0.674290123109141</v>
+        <v>0.5687702435318613</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6500362548772668</v>
+        <v>0.5628421821985187</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7078535083834971</v>
+        <v>0.5579539252710443</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1849259518783946</v>
+        <v>0.4256794586484524</v>
       </c>
       <c r="L18" t="n">
-        <v>1.766295909881592</v>
+        <v>4.703383493423462</v>
       </c>
     </row>
     <row r="19">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>discrete</t>
+          <t>lassocox</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1261,25 +1261,25 @@
         <v>100</v>
       </c>
       <c r="F19" t="n">
-        <v>2025</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6766392161454737</v>
+        <v>0.5687702435318613</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6419110917290799</v>
+        <v>0.5628421821985187</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7096684555716676</v>
+        <v>0.5764660681881931</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1879179357962965</v>
+        <v>0.4103826731553601</v>
       </c>
       <c r="L19" t="n">
-        <v>1.775444304943085</v>
+        <v>4.703383493423462</v>
       </c>
     </row>
     <row r="20">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>discrete</t>
+          <t>lassocox</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1305,25 +1305,25 @@
         <v>100</v>
       </c>
       <c r="F20" t="n">
-        <v>114514</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6783900235620515</v>
+        <v>0.5687702435318613</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6662895747221427</v>
+        <v>0.5628421821985187</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6985113835463259</v>
+        <v>0.587273538165716</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1878275685618645</v>
+        <v>0.356427200691689</v>
       </c>
       <c r="L20" t="n">
-        <v>1.76797525882721</v>
+        <v>4.703383493423462</v>
       </c>
     </row>
     <row r="21">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>discrete</t>
+          <t>lassocox</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1349,25 +1349,201 @@
         <v>100</v>
       </c>
       <c r="F21" t="n">
-        <v>777</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>25</v>
+        <v>10000</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6783579291711574</v>
+        <v>0.5687702435318613</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6481462203982711</v>
+        <v>0.5628421821985187</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7161476402726279</v>
+        <v>0.5741008515481989</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1928239435872588</v>
+        <v>0.4496883067288769</v>
       </c>
       <c r="L21" t="n">
-        <v>1.768315649032593</v>
+        <v>4.703383493423462</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>metabric</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>coxtime</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" t="n">
+        <v>42</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6513829672101475</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.6163182440318405</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.6834039181481758</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.276377250160539</v>
+      </c>
+      <c r="L22" t="n">
+        <v>4.577968311309815</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>metabric</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>coxtime</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42</v>
+      </c>
+      <c r="G23" t="n">
+        <v>100</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.6399204136316661</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.641802010778314</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5967949466801785</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.4445146764598201</v>
+      </c>
+      <c r="L23" t="n">
+        <v>4.822745370864868</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>metabric</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>coxtime</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" t="n">
+        <v>42</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4738866547822015</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5029157331133345</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5012499595147506</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.5494061556179434</v>
+      </c>
+      <c r="L24" t="n">
+        <v>6.117543840408326</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>metabric</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>coxtime</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" t="n">
+        <v>42</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4721021692252697</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.505619061973869</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5001976827979556</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.5520403729052233</v>
+      </c>
+      <c r="L25" t="n">
+        <v>5.373522233963013</v>
       </c>
     </row>
   </sheetData>
